--- a/templates/subject-gradebook-template.xlsx
+++ b/templates/subject-gradebook-template.xlsx
@@ -397,9 +397,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:X13"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -420,6 +420,9 @@
     <col min="19" max="19" width="14.83203125" customWidth="1"/>
     <col min="20" max="20" width="14.83203125" customWidth="1"/>
     <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,70 +489,88 @@
       <c r="U1" t="str">
         <v/>
       </c>
+      <c r="V1" t="str">
+        <v/>
+      </c>
+      <c r="W1" t="str">
+        <v/>
+      </c>
+      <c r="X1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>Student Name</v>
       </c>
       <c r="B2" t="str">
-        <v>Knowing and Understanding</v>
+        <v>Criterion A</v>
       </c>
       <c r="C2" t="str">
-        <v>Investigating Patterns</v>
+        <v>Criterion B</v>
       </c>
       <c r="D2" t="str">
-        <v>Communicating</v>
+        <v>Criterion C</v>
       </c>
       <c r="E2" t="str">
-        <v>Applying Mathematics in Real-World Contexts</v>
+        <v>Criterion D</v>
       </c>
       <c r="F2" t="str">
-        <v>Knowing and Understanding</v>
+        <v>Criterion A</v>
       </c>
       <c r="G2" t="str">
-        <v>Investigating Patterns</v>
+        <v>Criterion B</v>
       </c>
       <c r="H2" t="str">
-        <v>Communicating</v>
+        <v>Criterion C</v>
       </c>
       <c r="I2" t="str">
-        <v>Applying Mathematics in Real-World Contexts</v>
+        <v>Criterion D</v>
       </c>
       <c r="J2" t="str">
-        <v>Knowing and Understanding</v>
+        <v>Criterion A</v>
       </c>
       <c r="K2" t="str">
-        <v>Investigating Patterns</v>
+        <v>Criterion B</v>
       </c>
       <c r="L2" t="str">
-        <v>Communicating</v>
+        <v>Criterion C</v>
       </c>
       <c r="M2" t="str">
-        <v>Applying Mathematics in Real-World Contexts</v>
+        <v>Criterion D</v>
       </c>
       <c r="N2" t="str">
-        <v>Knowing and Understanding</v>
+        <v>Criterion A</v>
       </c>
       <c r="O2" t="str">
-        <v>Investigating Patterns</v>
+        <v>Criterion B</v>
       </c>
       <c r="P2" t="str">
-        <v>Communicating</v>
+        <v>Criterion C</v>
       </c>
       <c r="Q2" t="str">
-        <v>Applying Mathematics in Real-World Contexts</v>
+        <v>Criterion D</v>
       </c>
       <c r="R2" t="str">
-        <v>Knowing and Understanding</v>
+        <v>Criterion A</v>
       </c>
       <c r="S2" t="str">
-        <v>Investigating Patterns</v>
+        <v>Criterion B</v>
       </c>
       <c r="T2" t="str">
-        <v>Communicating</v>
+        <v>Criterion C</v>
       </c>
       <c r="U2" t="str">
-        <v>Applying Mathematics in Real-World Contexts</v>
+        <v>Criterion D</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Attendance %</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Homework %</v>
+      </c>
+      <c r="X2" t="str">
+        <v>EAL</v>
       </c>
     </row>
     <row r="3">
@@ -616,6 +637,15 @@
       <c r="U3" t="str">
         <v>4</v>
       </c>
+      <c r="V3">
+        <v>96</v>
+      </c>
+      <c r="W3">
+        <v>100</v>
+      </c>
+      <c r="X3" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -681,6 +711,15 @@
       <c r="U4" t="str">
         <v>7</v>
       </c>
+      <c r="V4">
+        <v>94</v>
+      </c>
+      <c r="W4">
+        <v>88</v>
+      </c>
+      <c r="X4" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -746,6 +785,15 @@
       <c r="U5" t="str">
         <v>7</v>
       </c>
+      <c r="V5">
+        <v>98</v>
+      </c>
+      <c r="W5">
+        <v>92</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -811,6 +859,15 @@
       <c r="U6" t="str">
         <v>3</v>
       </c>
+      <c r="V6">
+        <v>91</v>
+      </c>
+      <c r="W6">
+        <v>80</v>
+      </c>
+      <c r="X6" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -876,6 +933,15 @@
       <c r="U7" t="str">
         <v>5</v>
       </c>
+      <c r="V7">
+        <v>95</v>
+      </c>
+      <c r="W7">
+        <v>90</v>
+      </c>
+      <c r="X7" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -941,6 +1007,15 @@
       <c r="U8" t="str">
         <v>7</v>
       </c>
+      <c r="V8">
+        <v>95</v>
+      </c>
+      <c r="W8">
+        <v>90</v>
+      </c>
+      <c r="X8" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1006,6 +1081,15 @@
       <c r="U9" t="str">
         <v>6</v>
       </c>
+      <c r="V9">
+        <v>95</v>
+      </c>
+      <c r="W9">
+        <v>90</v>
+      </c>
+      <c r="X9" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1071,6 +1155,15 @@
       <c r="U10" t="str">
         <v>3</v>
       </c>
+      <c r="V10">
+        <v>95</v>
+      </c>
+      <c r="W10">
+        <v>90</v>
+      </c>
+      <c r="X10" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1136,6 +1229,15 @@
       <c r="U11" t="str">
         <v>-</v>
       </c>
+      <c r="V11">
+        <v>95</v>
+      </c>
+      <c r="W11">
+        <v>90</v>
+      </c>
+      <c r="X11" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1201,6 +1303,15 @@
       <c r="U12" t="str">
         <v/>
       </c>
+      <c r="V12">
+        <v>95</v>
+      </c>
+      <c r="W12">
+        <v>90</v>
+      </c>
+      <c r="X12" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1266,17 +1377,19 @@
       <c r="U13" t="str">
         <v/>
       </c>
+      <c r="V13">
+        <v>95</v>
+      </c>
+      <c r="W13">
+        <v>90</v>
+      </c>
+      <c r="X13" t="str">
+        <v>No</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="R1:U1"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X13"/>
   </ignoredErrors>
 </worksheet>
 </file>